--- a/sektorler/Teknoloji.xlsx
+++ b/sektorler/Teknoloji.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,40 +511,70 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>brüt_kar_marjı_%</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>net_kar_marjı_%</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>aktif_devir_hizi</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ozkaynak_carpani</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>roe_dupont_%</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Piotroski F-Skoru</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Sektör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F/K (PD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>FD/FAVÖK (PD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>FD/NS (PD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PD/DD (PD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin Fiyat</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>iskonto_%</t>
         </is>
@@ -553,233 +583,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZTEK</t>
+          <t>ESCOM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1878366533</v>
+        <v>3787777042</v>
       </c>
       <c r="C2" t="n">
-        <v>100000000</v>
+        <v>704842185</v>
       </c>
       <c r="D2" t="n">
-        <v>2103593622</v>
+        <v>-1076317</v>
       </c>
       <c r="E2" t="n">
-        <v>4.610000133514404</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="F2" t="n">
-        <v>461000013.3514404</v>
+        <v>3806147866.218989</v>
       </c>
       <c r="G2" t="n">
-        <v>2564593635.35144</v>
+        <v>3805071549.218989</v>
       </c>
       <c r="H2" t="n">
-        <v>9009234671</v>
+        <v>2304072539</v>
       </c>
       <c r="I2" t="n">
-        <v>403424321</v>
+        <v>2288910410</v>
       </c>
       <c r="J2" t="n">
-        <v>513286866</v>
+        <v>2289194274</v>
       </c>
       <c r="K2" t="n">
-        <v>-409740192</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>1394161082</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.730063200988843</v>
+      </c>
       <c r="M2" t="n">
-        <v>4.996413906588135</v>
+        <v>1.662188129874288</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2846627631541956</v>
+        <v>1.651454754488955</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2454260152384436</v>
+        <v>1.004850027869985</v>
       </c>
       <c r="P2" t="n">
-        <v>87.51069616400467</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>60.13719094612564</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" t="n">
+        <v>60.50855858058556</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.605803457767762</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.021957815053799</v>
+      </c>
+      <c r="U2" t="n">
+        <v>37.46118613714962</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>-11472469760.3937</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6094618879.070891</v>
-      </c>
-      <c r="T2" t="n">
-        <v>41833478646.0595</v>
-      </c>
-      <c r="U2" t="n">
-        <v>10657060340.5707</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11778172026.32685</v>
-      </c>
-      <c r="W2" t="n">
-        <v>117.7817202632685</v>
-      </c>
       <c r="X2" t="n">
-        <v>-96.08597996088865</v>
+        <v>71569574851.93544</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>58948329595.51793</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16822101868.68293</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>34863899431.82103</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>45550976436.98933</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>64.6257806447685</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-91.64420136748544</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESCOM</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3787777042</v>
+        <v>5256723777</v>
       </c>
       <c r="C3" t="n">
-        <v>704842185</v>
+        <v>93750000</v>
       </c>
       <c r="D3" t="n">
-        <v>-1076317</v>
+        <v>-447039696</v>
       </c>
       <c r="E3" t="n">
-        <v>5.610000133514404</v>
+        <v>243.1000061035156</v>
       </c>
       <c r="F3" t="n">
-        <v>3954164751.956584</v>
+        <v>22790625572.20459</v>
       </c>
       <c r="G3" t="n">
-        <v>3953088434.956584</v>
+        <v>22343585876.20459</v>
       </c>
       <c r="H3" t="n">
-        <v>2304072539</v>
+        <v>6877734978</v>
       </c>
       <c r="I3" t="n">
-        <v>2288910410</v>
+        <v>4789849532</v>
       </c>
       <c r="J3" t="n">
-        <v>2289194274</v>
+        <v>5073309029</v>
       </c>
       <c r="K3" t="n">
-        <v>1394161082</v>
+        <v>2547773716</v>
       </c>
       <c r="L3" t="n">
-        <v>2.836232342882588</v>
+        <v>8.945309950047616</v>
       </c>
       <c r="M3" t="n">
-        <v>1.726847074472712</v>
+        <v>4.404144464388903</v>
       </c>
       <c r="N3" t="n">
-        <v>1.715696171906237</v>
+        <v>3.248683752380054</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0439275353622</v>
+        <v>4.335518954205189</v>
       </c>
       <c r="P3" t="n">
-        <v>57.88606579600434</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>21.01675321208248</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>86.65141746611802</v>
+      </c>
+      <c r="R3" t="n">
+        <v>37.04379020345556</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8151912609013192</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.669388150283052</v>
+      </c>
+      <c r="U3" t="n">
+        <v>50.41180615484493</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>39035640551.37347</v>
-      </c>
-      <c r="S3" t="n">
-        <v>36564063522.84583</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11237791238.27506</v>
-      </c>
-      <c r="U3" t="n">
-        <v>21490251121.94246</v>
-      </c>
-      <c r="V3" t="n">
-        <v>27081936608.60921</v>
-      </c>
-      <c r="W3" t="n">
-        <v>38.42269544154654</v>
-      </c>
       <c r="X3" t="n">
-        <v>-85.39925408916444</v>
+        <v>130790540653.6486</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>131085856894.3759</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>50658373690.22086</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>48384550376.12807</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>90229830403.59335</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>962.4515243049958</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-74.74158438482783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>KFEIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4408500730</v>
+        <v>1396248544</v>
       </c>
       <c r="C4" t="n">
-        <v>93750000</v>
+        <v>197500000</v>
       </c>
       <c r="D4" t="n">
-        <v>-449801872</v>
+        <v>-252437621</v>
       </c>
       <c r="E4" t="n">
-        <v>144.1999969482422</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="F4" t="n">
-        <v>13518749713.89771</v>
+        <v>1658999924.659729</v>
       </c>
       <c r="G4" t="n">
-        <v>13068947841.89771</v>
+        <v>1406562303.659729</v>
       </c>
       <c r="H4" t="n">
-        <v>5660458720</v>
+        <v>3283075263</v>
       </c>
       <c r="I4" t="n">
-        <v>3741248062</v>
+        <v>235991603</v>
       </c>
       <c r="J4" t="n">
-        <v>4003883842</v>
+        <v>302445331</v>
       </c>
       <c r="K4" t="n">
-        <v>2053605858</v>
+        <v>57173699</v>
       </c>
       <c r="L4" t="n">
-        <v>6.582932971891486</v>
+        <v>29.0168373513795</v>
       </c>
       <c r="M4" t="n">
-        <v>3.264067679688123</v>
+        <v>4.650633220255362</v>
       </c>
       <c r="N4" t="n">
-        <v>2.308814265480184</v>
+        <v>0.4284282847583714</v>
       </c>
       <c r="O4" t="n">
-        <v>3.066518651545671</v>
+        <v>1.188183817121122</v>
       </c>
       <c r="P4" t="n">
-        <v>27.67451237116904</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>14.22493150796275</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17.90655836085839</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.741467813557097</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.488405151277977</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.565975364296071</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.059023278597983</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>57499682886.05759</v>
-      </c>
-      <c r="S4" t="n">
-        <v>64399793076.95741</v>
-      </c>
-      <c r="T4" t="n">
-        <v>28055252604.85366</v>
-      </c>
-      <c r="U4" t="n">
-        <v>25011975812.84845</v>
-      </c>
-      <c r="V4" t="n">
-        <v>43741676095.17928</v>
-      </c>
-      <c r="W4" t="n">
-        <v>466.577878348579</v>
-      </c>
       <c r="X4" t="n">
-        <v>-69.09412048024471</v>
+        <v>2935024785.136361</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8040471049.115324</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24220733736.79393</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>12851513771.81892</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12011935835.71614</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>60.81992828210702</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-86.18873804065053</v>
       </c>
     </row>
     <row r="5">
@@ -789,75 +875,93 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2466945149</v>
+        <v>2725996326</v>
       </c>
       <c r="C5" t="n">
         <v>67000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1294629297</v>
+        <v>1703516161</v>
       </c>
       <c r="E5" t="n">
-        <v>94.59999847412109</v>
+        <v>112.9000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>6338199897.766113</v>
+        <v>7564300102.233887</v>
       </c>
       <c r="G5" t="n">
-        <v>7632829194.766113</v>
+        <v>9267816263.233887</v>
       </c>
       <c r="H5" t="n">
-        <v>2437633702</v>
+        <v>3352540068</v>
       </c>
       <c r="I5" t="n">
-        <v>764722597</v>
+        <v>861125614</v>
       </c>
       <c r="J5" t="n">
-        <v>816381303</v>
+        <v>911123412</v>
       </c>
       <c r="K5" t="n">
-        <v>2329162169</v>
+        <v>2616948923</v>
       </c>
       <c r="L5" t="n">
-        <v>2.721235980098092</v>
+        <v>2.890503530944875</v>
       </c>
       <c r="M5" t="n">
-        <v>9.349588441966208</v>
+        <v>10.17185612966544</v>
       </c>
       <c r="N5" t="n">
-        <v>3.131245350153972</v>
+        <v>2.764416256108378</v>
       </c>
       <c r="O5" t="n">
-        <v>2.56925043523378</v>
+        <v>2.774875384125476</v>
       </c>
       <c r="P5" t="n">
-        <v>12.06529628813893</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+        <v>11.38407522654598</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>34.95369821781352</v>
+      </c>
+      <c r="R5" t="n">
+        <v>78.05869191478966</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5050895202007794</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.439982259559171</v>
+      </c>
+      <c r="U5" t="n">
+        <v>96.20027103630167</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>65215087688.79937</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11744604408.80681</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10593449106.88326</v>
-      </c>
-      <c r="U5" t="n">
-        <v>13996407435.87034</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25387387160.08994</v>
-      </c>
-      <c r="W5" t="n">
-        <v>378.9162262699991</v>
-      </c>
       <c r="X5" t="n">
-        <v>-75.03405979592088</v>
+        <v>134341665569.7038</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>21758110991.03063</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22771912104.5286</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>25090933470.30683</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>50990655533.89246</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>761.0545602073501</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-85.16532093374236</v>
       </c>
     </row>
     <row r="6">
@@ -867,465 +971,563 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3735786000</v>
+        <v>4102311000</v>
       </c>
       <c r="C6" t="n">
         <v>95000000</v>
       </c>
       <c r="D6" t="n">
-        <v>-1368287000</v>
+        <v>-1269260000</v>
       </c>
       <c r="E6" t="n">
-        <v>142.5</v>
+        <v>137.3000030517578</v>
       </c>
       <c r="F6" t="n">
-        <v>13537500000</v>
+        <v>13043500289.91699</v>
       </c>
       <c r="G6" t="n">
-        <v>12169213000</v>
+        <v>11774240289.91699</v>
       </c>
       <c r="H6" t="n">
-        <v>5800666000</v>
+        <v>6533563636</v>
       </c>
       <c r="I6" t="n">
-        <v>1252913000</v>
+        <v>1355198575</v>
       </c>
       <c r="J6" t="n">
-        <v>2010193000</v>
+        <v>2207307762</v>
       </c>
       <c r="K6" t="n">
-        <v>1500717000</v>
+        <v>826558514</v>
       </c>
       <c r="L6" t="n">
-        <v>9.020688111082903</v>
+        <v>15.78049232932708</v>
       </c>
       <c r="M6" t="n">
-        <v>6.053753545057614</v>
+        <v>5.33420871009332</v>
       </c>
       <c r="N6" t="n">
-        <v>2.097899275703859</v>
+        <v>1.802116110883318</v>
       </c>
       <c r="O6" t="n">
-        <v>3.623735406685501</v>
+        <v>3.179549353990224</v>
       </c>
       <c r="P6" t="n">
-        <v>9.255128347183748</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>10.38983819433506</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>96.48610037660005</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12.65095987503136</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7591918272636025</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.095643750273632</v>
+      </c>
+      <c r="U6" t="n">
+        <v>20.12762159896609</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>42019139780.67532</v>
-      </c>
-      <c r="S6" t="n">
-        <v>33475068750.70468</v>
-      </c>
-      <c r="T6" t="n">
-        <v>29657513616.0258</v>
-      </c>
-      <c r="U6" t="n">
-        <v>21195275853.78847</v>
-      </c>
-      <c r="V6" t="n">
-        <v>31586749500.29857</v>
-      </c>
-      <c r="W6" t="n">
-        <v>332.4921000031428</v>
-      </c>
       <c r="X6" t="n">
-        <v>-57.14183885913287</v>
+        <v>42431568490.18077</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>58107917683.21094</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>48967949604.79914</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>37758969589.8614</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>46816601342.01306</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>492.8063299159269</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-72.1391559489138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KFEIN</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1291226258</v>
+        <v>549820175</v>
       </c>
       <c r="C7" t="n">
-        <v>197500000</v>
+        <v>22750000</v>
       </c>
       <c r="D7" t="n">
-        <v>-353213171</v>
+        <v>-62227863</v>
       </c>
       <c r="E7" t="n">
-        <v>8.850000381469727</v>
+        <v>123.8000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>1747875075.340271</v>
+        <v>2816450069.42749</v>
       </c>
       <c r="G7" t="n">
-        <v>1394661904.340271</v>
+        <v>2754222206.42749</v>
       </c>
       <c r="H7" t="n">
-        <v>2844268102</v>
+        <v>2775595382</v>
       </c>
       <c r="I7" t="n">
-        <v>161244858</v>
+        <v>210915232</v>
       </c>
       <c r="J7" t="n">
-        <v>232502986</v>
+        <v>253189384</v>
       </c>
       <c r="K7" t="n">
-        <v>47295631</v>
+        <v>95032178</v>
       </c>
       <c r="L7" t="n">
-        <v>36.95637500513041</v>
+        <v>29.63680438248496</v>
       </c>
       <c r="M7" t="n">
-        <v>5.998468786720317</v>
+        <v>10.87811093385926</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4903412246403877</v>
+        <v>0.9922996068839439</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35365515107134</v>
+        <v>5.122493130463047</v>
       </c>
       <c r="P7" t="n">
-        <v>9.225193509244894</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>7.488690614098956</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10.33183985892653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.423848397222906</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.134627358734075</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.63924239978795</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17.59315079143737</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>1324248162.714383</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4066748452.383005</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14224403978.09208</v>
-      </c>
-      <c r="U7" t="n">
-        <v>7325873786.122931</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6735318594.8281</v>
-      </c>
-      <c r="W7" t="n">
-        <v>34.10287896115494</v>
-      </c>
       <c r="X7" t="n">
-        <v>-74.04911065851547</v>
+        <v>4878498377.64547</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6581909881.949492</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20325635395.30737</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5060719011.239584</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9211690666.535479</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>404.9094798477133</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-69.42526435826618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>NETCD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5049378101</v>
+        <v>3756403776</v>
       </c>
       <c r="C8" t="n">
-        <v>322274086</v>
+        <v>137000000</v>
       </c>
       <c r="D8" t="n">
-        <v>1439053464</v>
+        <v>-1022774234</v>
       </c>
       <c r="E8" t="n">
-        <v>50.54999923706055</v>
+        <v>132.1000061035156</v>
       </c>
       <c r="F8" t="n">
-        <v>16290954801.42439</v>
+        <v>18097700836.18164</v>
       </c>
       <c r="G8" t="n">
-        <v>17730008265.42439</v>
+        <v>17074926602.18164</v>
       </c>
       <c r="H8" t="n">
-        <v>4224605448</v>
+        <v>2019100165</v>
       </c>
       <c r="I8" t="n">
-        <v>1221377981</v>
+        <v>1263873944</v>
       </c>
       <c r="J8" t="n">
-        <v>1962856759</v>
+        <v>1595798133</v>
       </c>
       <c r="K8" t="n">
-        <v>541848691</v>
+        <v>1189209158</v>
       </c>
       <c r="L8" t="n">
-        <v>30.06550550368384</v>
+        <v>15.21826561327376</v>
       </c>
       <c r="M8" t="n">
-        <v>9.032757069067609</v>
+        <v>10.69992892527193</v>
       </c>
       <c r="N8" t="n">
-        <v>4.196843583065982</v>
+        <v>8.456701107833172</v>
       </c>
       <c r="O8" t="n">
-        <v>3.226328960827484</v>
+        <v>4.81782628156469</v>
       </c>
       <c r="P8" t="n">
-        <v>7.497276837900317</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>6.983616070574077</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>92.01782790206448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>58.89797735715603</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>15171425316.76855</v>
-      </c>
-      <c r="S8" t="n">
-        <v>29911674336.31994</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19163894694.32685</v>
-      </c>
-      <c r="U8" t="n">
-        <v>28648044010.22264</v>
-      </c>
-      <c r="V8" t="n">
-        <v>23223759589.4095</v>
-      </c>
-      <c r="W8" t="n">
-        <v>72.06213778358058</v>
-      </c>
       <c r="X8" t="n">
-        <v>-29.85220700935353</v>
+        <v>61048321422.07806</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>42114925212.94179</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>15763341161.4687</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>34575129956.0722</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>38375429438.14018</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>280.1126236360597</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-52.84039527074351</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MTRKS</t>
+          <t>AZTEK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>954835922</v>
+        <v>1914868068</v>
       </c>
       <c r="C9" t="n">
-        <v>100500000</v>
+        <v>1000000000</v>
       </c>
       <c r="D9" t="n">
-        <v>-205138663</v>
+        <v>2392115641</v>
       </c>
       <c r="E9" t="n">
-        <v>24.04000091552734</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="F9" t="n">
-        <v>2416020092.010498</v>
+        <v>4389999866.485596</v>
       </c>
       <c r="G9" t="n">
-        <v>2210881429.010498</v>
+        <v>6782115507.485596</v>
       </c>
       <c r="H9" t="n">
-        <v>1277007496</v>
+        <v>9979441402</v>
       </c>
       <c r="I9" t="n">
-        <v>173301877</v>
+        <v>299432580</v>
       </c>
       <c r="J9" t="n">
-        <v>350016427</v>
+        <v>405049858</v>
       </c>
       <c r="K9" t="n">
-        <v>241120644</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10.01996366603308</v>
-      </c>
+        <v>-607737148</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>6.316507622113685</v>
+        <v>16.7439029382047</v>
       </c>
       <c r="N9" t="n">
-        <v>1.731298708845244</v>
+        <v>0.6796087310183893</v>
       </c>
       <c r="O9" t="n">
-        <v>2.530298699854003</v>
+        <v>2.292586074126124</v>
       </c>
       <c r="P9" t="n">
-        <v>7.173031282856027</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>6.820787906759325</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.61889658260453</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-6.089891443004037</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.6790396999129</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.985334575026372</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-30.5255520467319</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>6751227609.364359</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5795597405.444361</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6432967406.235288</v>
-      </c>
-      <c r="U9" t="n">
-        <v>5417336743.029835</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6099282291.01846</v>
-      </c>
-      <c r="W9" t="n">
-        <v>60.68937603003443</v>
-      </c>
       <c r="X9" t="n">
-        <v>-60.38845266158241</v>
+        <v>-31198324114.52134</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8038006800.392111</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>70463419926.21791</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17625052110.43449</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16232038680.63079</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16.23203868063079</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-72.95472273779109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>NETCD</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3756403776</v>
+        <v>5879015160</v>
       </c>
       <c r="C10" t="n">
-        <v>137000000</v>
+        <v>322274086</v>
       </c>
       <c r="D10" t="n">
-        <v>-1022774234</v>
+        <v>1354558939</v>
       </c>
       <c r="E10" t="n">
-        <v>130.5</v>
+        <v>76.80000305175781</v>
       </c>
       <c r="F10" t="n">
-        <v>17878500000</v>
+        <v>24750650788.30246</v>
       </c>
       <c r="G10" t="n">
-        <v>16855725766</v>
+        <v>26105209727.30246</v>
       </c>
       <c r="H10" t="n">
-        <v>2019100165</v>
+        <v>5969265115</v>
       </c>
       <c r="I10" t="n">
-        <v>1263873944</v>
+        <v>1672724979</v>
       </c>
       <c r="J10" t="n">
-        <v>1595798133</v>
+        <v>2514467034</v>
       </c>
       <c r="K10" t="n">
-        <v>1189209158</v>
+        <v>784847121</v>
       </c>
       <c r="L10" t="n">
-        <v>15.03394073256876</v>
+        <v>31.53563302464157</v>
       </c>
       <c r="M10" t="n">
-        <v>10.56256766907748</v>
+        <v>10.38200516225279</v>
       </c>
       <c r="N10" t="n">
-        <v>8.348137481331937</v>
+        <v>4.373270281077549</v>
       </c>
       <c r="O10" t="n">
-        <v>4.759472374675837</v>
+        <v>4.209999483706461</v>
       </c>
       <c r="P10" t="n">
-        <v>7.069239276225635</v>
-      </c>
-      <c r="Q10" t="inlineStr">
+        <v>6.758307057487781</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>45.09395225613128</v>
+      </c>
+      <c r="R10" t="n">
+        <v>13.14813642684054</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6611711759984936</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.579018199398991</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13.72667178279041</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>33297114538.22486</v>
-      </c>
-      <c r="S10" t="n">
-        <v>26510845466.17174</v>
-      </c>
-      <c r="T10" t="n">
-        <v>10869709418.36333</v>
-      </c>
-      <c r="U10" t="n">
-        <v>21312252428.41336</v>
-      </c>
-      <c r="V10" t="n">
-        <v>22997480462.79332</v>
-      </c>
-      <c r="W10" t="n">
-        <v>167.8648208963016</v>
-      </c>
       <c r="X10" t="n">
-        <v>-22.25887514536695</v>
+        <v>40290304684.99015</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>63393517184.17213</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>42224434050.41498</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>54112317336.44137</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>50005143314.00466</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>155.1634012360667</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-50.5037899144053</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>910736868</v>
+        <v>1966732279</v>
       </c>
       <c r="C11" t="n">
-        <v>117000000</v>
+        <v>891754956</v>
       </c>
       <c r="D11" t="n">
-        <v>332241776</v>
+        <v>-645400947</v>
       </c>
       <c r="E11" t="n">
-        <v>21.20000076293945</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="F11" t="n">
-        <v>2480400089.263916</v>
+        <v>5305941818.11124</v>
       </c>
       <c r="G11" t="n">
-        <v>2812641865.263916</v>
+        <v>4660540871.11124</v>
       </c>
       <c r="H11" t="n">
-        <v>2427624044</v>
+        <v>1609405370</v>
       </c>
       <c r="I11" t="n">
-        <v>145514138</v>
+        <v>340182033</v>
       </c>
       <c r="J11" t="n">
-        <v>487132951</v>
+        <v>481785209</v>
       </c>
       <c r="K11" t="n">
-        <v>175035357</v>
+        <v>483747350</v>
       </c>
       <c r="L11" t="n">
-        <v>14.17085171691292</v>
+        <v>10.96841526493373</v>
       </c>
       <c r="M11" t="n">
-        <v>5.773869042301587</v>
+        <v>9.67348267246461</v>
       </c>
       <c r="N11" t="n">
-        <v>1.158598619178908</v>
+        <v>2.895815409831297</v>
       </c>
       <c r="O11" t="n">
-        <v>2.723509035832637</v>
+        <v>2.697846511579648</v>
       </c>
       <c r="P11" t="n">
-        <v>5.866559134142864</v>
-      </c>
-      <c r="Q11" t="inlineStr">
+        <v>6.411341184308252</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>34.72849571764508</v>
+      </c>
+      <c r="R11" t="n">
+        <v>30.05752056114986</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6789768959249785</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.263252806252057</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.7809205799013</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>4900880800.539614</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7448240665.901707</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11507020598.22203</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5167137289.843513</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7255819838.626715</v>
-      </c>
-      <c r="W11" t="n">
-        <v>62.01555417629671</v>
-      </c>
       <c r="X11" t="n">
-        <v>-65.81502649694548</v>
+        <v>24833279756.7293</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13051475461.21866</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12394965421.88207</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>18102426733.16572</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17095536843.24894</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19.17066647987201</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-68.9629997188034</v>
       </c>
     </row>
     <row r="12">
@@ -1335,1036 +1537,1528 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1691187591</v>
+        <v>1876232593</v>
       </c>
       <c r="C12" t="n">
         <v>936000000</v>
       </c>
       <c r="D12" t="n">
-        <v>-89133745</v>
+        <v>-82849116</v>
       </c>
       <c r="E12" t="n">
-        <v>4.920000076293945</v>
+        <v>5.070000171661377</v>
       </c>
       <c r="F12" t="n">
-        <v>4605120071.411133</v>
+        <v>4745520160.675049</v>
       </c>
       <c r="G12" t="n">
-        <v>4515986326.411133</v>
+        <v>4662671044.675049</v>
       </c>
       <c r="H12" t="n">
-        <v>855070469</v>
+        <v>983706776</v>
       </c>
       <c r="I12" t="n">
-        <v>229835841</v>
+        <v>264901368</v>
       </c>
       <c r="J12" t="n">
-        <v>378008331</v>
+        <v>434203494</v>
       </c>
       <c r="K12" t="n">
-        <v>222880797</v>
+        <v>264762985</v>
       </c>
       <c r="L12" t="n">
-        <v>20.66180726826427</v>
+        <v>17.92365409641778</v>
       </c>
       <c r="M12" t="n">
-        <v>11.9467904701051</v>
+        <v>10.73844662492525</v>
       </c>
       <c r="N12" t="n">
-        <v>5.281420058504128</v>
+        <v>4.739899285470663</v>
       </c>
       <c r="O12" t="n">
-        <v>2.723009615206627</v>
+        <v>2.529281379281022</v>
       </c>
       <c r="P12" t="n">
-        <v>4.9908761864177</v>
-      </c>
-      <c r="Q12" t="inlineStr">
+        <v>5.582135551655056</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>40.39202877260652</v>
+      </c>
+      <c r="R12" t="n">
+        <v>26.91482781856938</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4808638034538582</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.09477559772796</v>
+      </c>
+      <c r="U12" t="n">
+        <v>14.16898699274419</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>6240523272.256742</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6126678887.861971</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4259220812.625073</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9595085883.331913</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6555377214.018925</v>
-      </c>
-      <c r="W12" t="n">
-        <v>7.003608134635603</v>
-      </c>
       <c r="X12" t="n">
-        <v>-29.7504945777505</v>
+        <v>13591667790.49378</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11263684061.26312</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7264461905.691619</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>17269438963.20727</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12347313180.16395</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13.19157391043157</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-61.56637406509813</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>482107005</v>
+        <v>5647873743</v>
       </c>
       <c r="C13" t="n">
-        <v>22750000</v>
+        <v>494000000</v>
       </c>
       <c r="D13" t="n">
-        <v>-72959879</v>
+        <v>1171448116</v>
       </c>
       <c r="E13" t="n">
-        <v>136.6999969482422</v>
+        <v>30.13999938964844</v>
       </c>
       <c r="F13" t="n">
-        <v>3109924930.57251</v>
+        <v>14889159698.48633</v>
       </c>
       <c r="G13" t="n">
-        <v>3036965051.57251</v>
+        <v>16060607814.48633</v>
       </c>
       <c r="H13" t="n">
-        <v>2285190126</v>
+        <v>2769003292</v>
       </c>
       <c r="I13" t="n">
-        <v>152961921</v>
+        <v>778225392</v>
       </c>
       <c r="J13" t="n">
-        <v>189886846</v>
+        <v>1255432771</v>
       </c>
       <c r="K13" t="n">
-        <v>68884267</v>
-      </c>
-      <c r="L13" t="n">
-        <v>45.14710057918609</v>
-      </c>
+        <v>-1060540747</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>15.99355150473409</v>
+        <v>12.79288559728566</v>
       </c>
       <c r="N13" t="n">
-        <v>1.328976970895817</v>
+        <v>5.80014038296287</v>
       </c>
       <c r="O13" t="n">
-        <v>6.45069434444851</v>
+        <v>2.636241597457808</v>
       </c>
       <c r="P13" t="n">
-        <v>4.918508466114037</v>
-      </c>
-      <c r="Q13" t="inlineStr">
+        <v>5.226791892621828</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>33.84858496585709</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-38.3004509262967</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3537050959460146</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.342997807651061</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-18.1936781514624</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>1928716502.686623</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3105830614.223767</v>
-      </c>
-      <c r="T13" t="n">
-        <v>11217587295.07921</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2735272031.647096</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4746851610.909175</v>
-      </c>
-      <c r="W13" t="n">
-        <v>208.6528180619418</v>
-      </c>
       <c r="X13" t="n">
-        <v>-34.48447127722918</v>
+        <v>-54443099406.46014</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>31156220342.20295</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19043833451.32489</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>51984818535.0437</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11935443230.52785</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>24.16081625612925</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>24.74743845627465</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>740031907</v>
+        <v>1056734129</v>
       </c>
       <c r="C14" t="n">
-        <v>171222156</v>
+        <v>117000000</v>
       </c>
       <c r="D14" t="n">
-        <v>-43332917</v>
+        <v>348412479</v>
       </c>
       <c r="E14" t="n">
-        <v>19.48999977111816</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>3337119781.250359</v>
+        <v>3861000000</v>
       </c>
       <c r="G14" t="n">
-        <v>3293786864.250359</v>
+        <v>4209412479</v>
       </c>
       <c r="H14" t="n">
-        <v>536690451</v>
+        <v>2784844334</v>
       </c>
       <c r="I14" t="n">
-        <v>143391846</v>
+        <v>197197689</v>
       </c>
       <c r="J14" t="n">
-        <v>215368617</v>
+        <v>645460893</v>
       </c>
       <c r="K14" t="n">
-        <v>146894731</v>
+        <v>147651928</v>
       </c>
       <c r="L14" t="n">
-        <v>22.71776365654912</v>
+        <v>26.14933683764698</v>
       </c>
       <c r="M14" t="n">
-        <v>15.29371785978622</v>
+        <v>6.52156083296591</v>
       </c>
       <c r="N14" t="n">
-        <v>6.137219058235785</v>
+        <v>1.511543186672063</v>
       </c>
       <c r="O14" t="n">
-        <v>4.509426890495356</v>
+        <v>3.653709948455729</v>
       </c>
       <c r="P14" t="n">
-        <v>4.296874412649151</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+        <v>5.107425252525252</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>31.55542068442236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.301981378180688</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.075399020037893</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.515497050898539</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14.34272418732495</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>4112960828.013343</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3483198234.394949</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2660714747.120212</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4198629260.20659</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3613875767.433774</v>
-      </c>
-      <c r="W14" t="n">
-        <v>21.10635592880733</v>
-      </c>
       <c r="X14" t="n">
-        <v>-7.658148868242387</v>
+        <v>7579745159.626098</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16272346699.54116</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19982517605.34725</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9726515576.581022</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13390281260.27388</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>114.4468483784092</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-71.16565421628023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>MTRKS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5462068845</v>
+        <v>1139133952</v>
       </c>
       <c r="C15" t="n">
-        <v>494000000</v>
+        <v>100500000</v>
       </c>
       <c r="D15" t="n">
-        <v>394955118</v>
+        <v>-176955584</v>
       </c>
       <c r="E15" t="n">
-        <v>39.34000015258789</v>
+        <v>27.26000022888184</v>
       </c>
       <c r="F15" t="n">
-        <v>19433960075.37842</v>
+        <v>2739630023.002625</v>
       </c>
       <c r="G15" t="n">
-        <v>19828915193.37842</v>
+        <v>2562674439.002625</v>
       </c>
       <c r="H15" t="n">
-        <v>2757037061</v>
+        <v>1441671175</v>
       </c>
       <c r="I15" t="n">
-        <v>785249566</v>
+        <v>136776305</v>
       </c>
       <c r="J15" t="n">
-        <v>1184849544</v>
+        <v>343199494</v>
       </c>
       <c r="K15" t="n">
-        <v>-729884911</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>269863384</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10.15191458135211</v>
+      </c>
       <c r="M15" t="n">
-        <v>16.73538660987865</v>
+        <v>7.467011122698871</v>
       </c>
       <c r="N15" t="n">
-        <v>7.192110499300401</v>
+        <v>1.777572086785064</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55798519331523</v>
+        <v>2.405011296689561</v>
       </c>
       <c r="P15" t="n">
-        <v>4.040605017990445</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+        <v>4.992510078061332</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16.0588891568842</v>
+      </c>
+      <c r="R15" t="n">
+        <v>18.71878890829596</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.047658651726009</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.256795496509028</v>
+      </c>
+      <c r="U15" t="n">
+        <v>24.64689224731246</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>-20436322170.74556</v>
-      </c>
-      <c r="S15" t="n">
-        <v>18529449512.11759</v>
-      </c>
-      <c r="T15" t="n">
-        <v>13050819247.80743</v>
-      </c>
-      <c r="U15" t="n">
-        <v>30989477422.46445</v>
-      </c>
-      <c r="V15" t="n">
-        <v>10533356002.91098</v>
-      </c>
-      <c r="W15" t="n">
-        <v>21.32258300184408</v>
-      </c>
       <c r="X15" t="n">
-        <v>84.49922389414817</v>
+        <v>13853497928.143</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9014417623.657887</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>10701966086.63147</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>10484949642.37149</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11013707820.20096</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>109.589132539313</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-75.12527054714771</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1623064025</v>
+        <v>1774061912</v>
       </c>
       <c r="C16" t="n">
-        <v>891754956</v>
+        <v>170000000</v>
       </c>
       <c r="D16" t="n">
-        <v>-655187907</v>
+        <v>-395892139</v>
       </c>
       <c r="E16" t="n">
-        <v>5.369999885559082</v>
+        <v>62.90000152587891</v>
       </c>
       <c r="F16" t="n">
-        <v>4788724011.666744</v>
+        <v>10693000259.39941</v>
       </c>
       <c r="G16" t="n">
-        <v>4133536104.666744</v>
+        <v>10297108120.39941</v>
       </c>
       <c r="H16" t="n">
-        <v>1425172790</v>
+        <v>5059746202</v>
       </c>
       <c r="I16" t="n">
-        <v>189998916</v>
+        <v>500271367</v>
       </c>
       <c r="J16" t="n">
-        <v>299781705</v>
+        <v>544257176</v>
       </c>
       <c r="K16" t="n">
-        <v>320192261</v>
+        <v>86123197</v>
       </c>
       <c r="L16" t="n">
-        <v>14.95577687202985</v>
+        <v>124.1593511606335</v>
       </c>
       <c r="M16" t="n">
-        <v>13.78848687469685</v>
+        <v>18.91956335068959</v>
       </c>
       <c r="N16" t="n">
-        <v>2.900375402667311</v>
+        <v>2.0351036809572</v>
       </c>
       <c r="O16" t="n">
-        <v>2.950422126241597</v>
+        <v>6.027410986657502</v>
       </c>
       <c r="P16" t="n">
-        <v>3.967631367711035</v>
-      </c>
-      <c r="Q16" t="inlineStr">
+        <v>4.678493919985169</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20.48232716870964</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.702124841083086</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>8965183556.692884</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5443298190.58428</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7605602915.087648</v>
-      </c>
-      <c r="U16" t="n">
-        <v>9208581470.736073</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7805666533.275222</v>
-      </c>
-      <c r="W16" t="n">
-        <v>8.753151839253945</v>
-      </c>
       <c r="X16" t="n">
-        <v>-38.65067139042362</v>
+        <v>4421153820.573713</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14410633468.16816</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>37334885468.52932</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>16329027659.22412</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18123925104.12383</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>106.6113241419049</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-41.0006375662721</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>710412391</v>
+        <v>824789585</v>
       </c>
       <c r="C17" t="n">
-        <v>45500000</v>
+        <v>171222156</v>
       </c>
       <c r="D17" t="n">
-        <v>98917743</v>
+        <v>-30035600</v>
       </c>
       <c r="E17" t="n">
-        <v>38.79999923706055</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="F17" t="n">
-        <v>1765399965.286255</v>
+        <v>4177820541.083931</v>
       </c>
       <c r="G17" t="n">
-        <v>1864317708.286255</v>
+        <v>4147784941.083931</v>
       </c>
       <c r="H17" t="n">
-        <v>855955349</v>
+        <v>605924726</v>
       </c>
       <c r="I17" t="n">
-        <v>44483608</v>
+        <v>168708448</v>
       </c>
       <c r="J17" t="n">
-        <v>211735481</v>
+        <v>256037505</v>
       </c>
       <c r="K17" t="n">
-        <v>6647663</v>
+        <v>144382011</v>
       </c>
       <c r="L17" t="n">
-        <v>265.567006824241</v>
+        <v>28.93587997665395</v>
       </c>
       <c r="M17" t="n">
-        <v>8.80493764900109</v>
+        <v>16.19991157578235</v>
       </c>
       <c r="N17" t="n">
-        <v>2.178054860530178</v>
+        <v>6.845379901337663</v>
       </c>
       <c r="O17" t="n">
-        <v>2.485035435264888</v>
+        <v>5.065316799658583</v>
       </c>
       <c r="P17" t="n">
-        <v>2.519746735850145</v>
-      </c>
-      <c r="Q17" t="inlineStr">
+        <v>4.038192793131051</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>90.07760165245344</v>
+      </c>
+      <c r="R17" t="n">
+        <v>23.8283741865322</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4632215301938782</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.596058002132461</v>
+      </c>
+      <c r="U17" t="n">
+        <v>17.61699447740051</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>186130416.8686191</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3282919163.877836</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4075484789.581682</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4030580605.311555</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2893778743.909923</v>
-      </c>
-      <c r="W17" t="n">
-        <v>63.59953283318512</v>
-      </c>
       <c r="X17" t="n">
-        <v>-38.99326377313359</v>
+        <v>7411883229.959124</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6623057357.678396</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4453626926.194128</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7591624539.936002</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6520048013.441913</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>38.07946451417136</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-35.9234696972964</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>919494030</v>
+        <v>2885058804</v>
       </c>
       <c r="C18" t="n">
-        <v>402170000</v>
+        <v>92600000</v>
       </c>
       <c r="D18" t="n">
-        <v>-314895529</v>
+        <v>-3632393945</v>
       </c>
       <c r="E18" t="n">
-        <v>19.70000076293945</v>
+        <v>136.8000030517578</v>
       </c>
       <c r="F18" t="n">
-        <v>7922749306.83136</v>
+        <v>12667680282.59277</v>
       </c>
       <c r="G18" t="n">
-        <v>7607853777.83136</v>
+        <v>9035286337.592773</v>
       </c>
       <c r="H18" t="n">
-        <v>2632002603</v>
+        <v>3556533219</v>
       </c>
       <c r="I18" t="n">
-        <v>49331232</v>
+        <v>400117787</v>
       </c>
       <c r="J18" t="n">
-        <v>69971814</v>
+        <v>706536479</v>
       </c>
       <c r="K18" t="n">
-        <v>-73699640</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>962193004</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13.1654254707019</v>
+      </c>
       <c r="M18" t="n">
-        <v>108.7274052639447</v>
+        <v>12.78813848420242</v>
       </c>
       <c r="N18" t="n">
-        <v>2.890519093392918</v>
+        <v>2.540475733313479</v>
       </c>
       <c r="O18" t="n">
-        <v>8.616422780723612</v>
+        <v>4.390787551723252</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6226529464647371</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+        <v>3.158571877992688</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>33.22530330061849</v>
+      </c>
+      <c r="R18" t="n">
+        <v>27.05423919168516</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>-2063543942.625725</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1432484616.614424</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13150890238.95861</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5216821737.583912</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4434163162.632806</v>
-      </c>
-      <c r="W18" t="n">
-        <v>11.02559405881295</v>
-      </c>
       <c r="X18" t="n">
-        <v>78.67518664169293</v>
+        <v>49394395748.73072</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21825862822.30563</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>29597086956.86709</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>26554994890.73302</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>31843085104.65912</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>343.8778089056061</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-60.21842657218129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>PAPIL</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>495363523</v>
+        <v>765978559</v>
       </c>
       <c r="C19" t="n">
-        <v>206250000</v>
+        <v>45500000</v>
       </c>
       <c r="D19" t="n">
-        <v>-153972237</v>
+        <v>49560918</v>
       </c>
       <c r="E19" t="n">
-        <v>16.29000091552734</v>
+        <v>41.72000122070312</v>
       </c>
       <c r="F19" t="n">
-        <v>3359812688.827515</v>
+        <v>1898260055.541992</v>
       </c>
       <c r="G19" t="n">
-        <v>3205840451.827515</v>
+        <v>1947820973.541992</v>
       </c>
       <c r="H19" t="n">
-        <v>137595692</v>
+        <v>922271164</v>
       </c>
       <c r="I19" t="n">
-        <v>3050568</v>
+        <v>42825363</v>
       </c>
       <c r="J19" t="n">
-        <v>30224846</v>
+        <v>233908370</v>
       </c>
       <c r="K19" t="n">
-        <v>-89267636</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>7836924</v>
+      </c>
+      <c r="L19" t="n">
+        <v>242.2200413761818</v>
+      </c>
       <c r="M19" t="n">
-        <v>106.0663949066114</v>
+        <v>8.32728206152688</v>
       </c>
       <c r="N19" t="n">
-        <v>23.29898854556809</v>
+        <v>2.111982949888686</v>
       </c>
       <c r="O19" t="n">
-        <v>6.782519367756343</v>
+        <v>2.478215653999778</v>
       </c>
       <c r="P19" t="n">
-        <v>0.09079577591167939</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+        <v>2.256032458512249</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23.01022305409518</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8497418444712428</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6778962658947904</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75805993428319</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.012707259788644</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>-2499438118.56229</v>
-      </c>
-      <c r="S19" t="n">
-        <v>636723163.8864529</v>
-      </c>
-      <c r="T19" t="n">
-        <v>825011685.2938491</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2810483929.724425</v>
-      </c>
-      <c r="V19" t="n">
-        <v>443195165.0856092</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.148825042839317</v>
-      </c>
       <c r="X19" t="n">
-        <v>658.0887503992786</v>
+        <v>402310268.2096884</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5973630773.049671</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6683537347.19501</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7050309231.983351</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5027446905.10943</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>110.4933385738336</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-62.24206657234357</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMART</t>
+          <t>DOFRB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>426986134</v>
+        <v>2142280161</v>
       </c>
       <c r="C20" t="n">
-        <v>31862500</v>
+        <v>155000000</v>
       </c>
       <c r="D20" t="n">
-        <v>88297110</v>
+        <v>-184365860</v>
       </c>
       <c r="E20" t="n">
-        <v>35.93999862670898</v>
+        <v>134.8000030517578</v>
       </c>
       <c r="F20" t="n">
-        <v>1145138206.243515</v>
+        <v>20894000473.02246</v>
       </c>
       <c r="G20" t="n">
-        <v>1233435316.243515</v>
+        <v>20709634613.02246</v>
       </c>
       <c r="H20" t="n">
-        <v>200120352</v>
+        <v>1197732591</v>
       </c>
       <c r="I20" t="n">
-        <v>226460</v>
+        <v>258629479</v>
       </c>
       <c r="J20" t="n">
-        <v>115636931</v>
+        <v>347193059</v>
       </c>
       <c r="K20" t="n">
-        <v>-20396425</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>265234833</v>
+      </c>
+      <c r="L20" t="n">
+        <v>78.77547694884578</v>
+      </c>
       <c r="M20" t="n">
-        <v>10.66644804196261</v>
+        <v>59.64875758942652</v>
       </c>
       <c r="N20" t="n">
-        <v>6.163467652922752</v>
+        <v>17.29069975104523</v>
       </c>
       <c r="O20" t="n">
-        <v>2.681909586889571</v>
+        <v>9.753159672294823</v>
       </c>
       <c r="P20" t="n">
-        <v>0.01977577892042168</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+        <v>1.237816948142279</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>66.96552269069883</v>
+      </c>
+      <c r="R20" t="n">
+        <v>22.14474541254259</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3297505491360098</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.644996869947797</v>
+      </c>
+      <c r="U20" t="n">
+        <v>12.01216516823419</v>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>-571087175.7307079</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1758654752.800386</v>
-      </c>
-      <c r="T20" t="n">
-        <v>887668406.4091247</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2422539432.363815</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1124443853.960654</v>
-      </c>
-      <c r="W20" t="n">
-        <v>35.29050934360626</v>
-      </c>
       <c r="X20" t="n">
-        <v>1.840407790034893</v>
+        <v>13615890214.42366</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9124663071.933538</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8928487486.499887</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>19718225032.71019</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12846816451.39182</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>82.88268678317301</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>62.63951891955936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>614310579</v>
+        <v>919494030</v>
       </c>
       <c r="C21" t="n">
-        <v>165528000</v>
+        <v>402170000</v>
       </c>
       <c r="D21" t="n">
-        <v>665334035</v>
+        <v>-314895529</v>
       </c>
       <c r="E21" t="n">
-        <v>30.15999984741211</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="F21" t="n">
-        <v>4992324454.742432</v>
+        <v>7359710693.16864</v>
       </c>
       <c r="G21" t="n">
-        <v>5657658489.742432</v>
+        <v>7044815164.16864</v>
       </c>
       <c r="H21" t="n">
-        <v>516521422</v>
+        <v>2632002603</v>
       </c>
       <c r="I21" t="n">
-        <v>-62248802</v>
+        <v>49331232</v>
       </c>
       <c r="J21" t="n">
-        <v>53132035</v>
+        <v>69971814</v>
       </c>
       <c r="K21" t="n">
-        <v>-410744113</v>
+        <v>-73699640</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>106.4830001286876</v>
+        <v>100.6807564567161</v>
       </c>
       <c r="N21" t="n">
-        <v>10.95338595606676</v>
+        <v>2.676598859035642</v>
       </c>
       <c r="O21" t="n">
-        <v>8.126710861579403</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+        <v>8.004087523187769</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.6702876520104216</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11.28486155984246</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-2.800135528589369</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.850211780464888</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.498600675987305</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-7.764015933787433</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>-11500578922.09957</v>
-      </c>
-      <c r="S21" t="n">
-        <v>183290277.0515306</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1853685601.536545</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3485339412.323274</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1494565907.797055</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>-3783387708.667007</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2116685044.665784</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>19529995005.15369</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8463314243.320192</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6581651646.118164</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>16.36534710723864</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>11.82163822829141</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ODINE</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2151179463</v>
+        <v>739991756</v>
       </c>
       <c r="C22" t="n">
-        <v>110500000</v>
+        <v>331056000</v>
       </c>
       <c r="D22" t="n">
-        <v>-527272551</v>
+        <v>780961566</v>
       </c>
       <c r="E22" t="n">
-        <v>1132</v>
+        <v>30.23999977111816</v>
       </c>
       <c r="F22" t="n">
-        <v>125086000000</v>
+        <v>10011133364.22729</v>
       </c>
       <c r="G22" t="n">
-        <v>124558727449</v>
+        <v>10792094930.22729</v>
       </c>
       <c r="H22" t="n">
-        <v>1883544167</v>
+        <v>535106846</v>
       </c>
       <c r="I22" t="n">
-        <v>-189170053</v>
+        <v>-105490238</v>
       </c>
       <c r="J22" t="n">
-        <v>34625815</v>
+        <v>19399197</v>
       </c>
       <c r="K22" t="n">
-        <v>16260661</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7692.553211705232</v>
-      </c>
+        <v>-489022149</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>3597.279297223762</v>
+        <v>556.3165800227347</v>
       </c>
       <c r="N22" t="n">
-        <v>66.12997434904324</v>
+        <v>20.16811223945226</v>
       </c>
       <c r="O22" t="n">
-        <v>58.14763582093569</v>
+        <v>13.52870931744177</v>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="n">
+        <v>25.54337269682399</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-91.38775791330467</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2686367162061902</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.813506786357836</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-69.07189317721453</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>455288363.8188784</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1080315709.117293</v>
-      </c>
-      <c r="T22" t="n">
-        <v>9713115656.180775</v>
-      </c>
-      <c r="U22" t="n">
-        <v>12204885967.58207</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5863401424.174754</v>
-      </c>
-      <c r="W22" t="n">
-        <v>53.06245632737334</v>
-      </c>
       <c r="X22" t="n">
-        <v>2033.335089156125</v>
-      </c>
+        <v>-25104062757.87135</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-281427999.9996225</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3125619401.868766</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6811118467.505787</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-3862188222.124104</v>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PATEK</t>
+          <t>ODINE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4244644666</v>
+        <v>2222618346</v>
       </c>
       <c r="C23" t="n">
-        <v>600000000</v>
+        <v>110500000</v>
       </c>
       <c r="D23" t="n">
-        <v>-3740607876</v>
+        <v>-626434560</v>
       </c>
       <c r="E23" t="n">
-        <v>21.71999931335449</v>
+        <v>2905</v>
       </c>
       <c r="F23" t="n">
-        <v>13031999588.0127</v>
+        <v>321002500000</v>
       </c>
       <c r="G23" t="n">
-        <v>9291391712.012695</v>
+        <v>320376065440</v>
       </c>
       <c r="H23" t="n">
-        <v>2990786828</v>
+        <v>2485692733</v>
       </c>
       <c r="I23" t="n">
-        <v>-441459330</v>
+        <v>-197908831</v>
       </c>
       <c r="J23" t="n">
-        <v>-226212797</v>
+        <v>63179811</v>
       </c>
       <c r="K23" t="n">
-        <v>1165805522</v>
+        <v>30006977</v>
       </c>
       <c r="L23" t="n">
-        <v>11.17853650723461</v>
-      </c>
-      <c r="M23" t="inlineStr"/>
+        <v>10697.59542922301</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5070.861409192883</v>
+      </c>
       <c r="N23" t="n">
-        <v>3.106671336460993</v>
+        <v>128.8880404189523</v>
       </c>
       <c r="O23" t="n">
-        <v>3.070221564693089</v>
+        <v>144.4253803527274</v>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="n">
+        <v>14.93406252799308</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.207187702712731</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.722050069769777</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.500093292056263</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.30755626547099</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>32641827330.53678</v>
-      </c>
-      <c r="S23" t="n">
-        <v>127539428.0970063</v>
-      </c>
-      <c r="T23" t="n">
-        <v>18326354812.2168</v>
-      </c>
-      <c r="U23" t="n">
-        <v>24082325539.30601</v>
-      </c>
-      <c r="V23" t="n">
-        <v>18794511777.53915</v>
-      </c>
-      <c r="W23" t="n">
-        <v>31.32418629589858</v>
-      </c>
       <c r="X23" t="n">
-        <v>-30.660611234462</v>
+        <v>1540414959.368236</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2253328512.778554</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>18773389687.36441</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>20457683129.45606</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10756204072.24182</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>97.34121332345535</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2884.347431901192</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SEKTÖR TOPLAM</t>
+          <t>PAPIL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>47800806538</v>
+        <v>427961966</v>
       </c>
       <c r="C24" t="n">
-        <v>6012403883</v>
+        <v>206250000</v>
       </c>
       <c r="D24" t="n">
-        <v>-2580631733</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>-5456655</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11.60999965667725</v>
+      </c>
       <c r="F24" t="n">
-        <v>271201637515.2339</v>
+        <v>2394562429.189682</v>
       </c>
       <c r="G24" t="n">
-        <v>268621005782.2339</v>
+        <v>2389105774.189682</v>
       </c>
       <c r="H24" t="n">
-        <v>55080358197</v>
+        <v>113623034</v>
       </c>
       <c r="I24" t="n">
-        <v>12322182961</v>
+        <v>-30806580</v>
       </c>
       <c r="J24" t="n">
-        <v>16818255709</v>
+        <v>-20720462</v>
       </c>
       <c r="K24" t="n">
-        <v>9685988575</v>
-      </c>
-      <c r="L24" t="n">
-        <v>27.9993761519829</v>
-      </c>
-      <c r="M24" t="n">
-        <v>15.97198963020202</v>
-      </c>
+        <v>-6185540</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>4.876892862996387</v>
+        <v>21.02659724954785</v>
       </c>
       <c r="O24" t="n">
-        <v>5.673578693690825</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.04543550353860914</v>
-      </c>
-      <c r="Q24" t="inlineStr">
+        <v>5.595269251542979</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>43.85044937279179</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-5.44391377544099</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1490960031538172</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.566355691346862</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.271357322483339</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>-317536096.6141506</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-528099773.7550311</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>834968714.981953</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3939097464.773221</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>982107577.346498</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.761733708346657</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>143.8187510638516</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>SMART</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>447890029</v>
+      </c>
+      <c r="C25" t="n">
+        <v>31862500</v>
+      </c>
+      <c r="D25" t="n">
+        <v>109840829</v>
+      </c>
+      <c r="E25" t="n">
+        <v>24.07999992370605</v>
+      </c>
+      <c r="F25" t="n">
+        <v>767248997.5690842</v>
+      </c>
+      <c r="G25" t="n">
+        <v>877089826.5690842</v>
+      </c>
+      <c r="H25" t="n">
+        <v>188232122</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-23072650</v>
+      </c>
+      <c r="J25" t="n">
+        <v>104008284</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-44498120</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>8.432884313033028</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.659618226952168</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.713029868698158</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>71.3686115699211</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-23.64002462874004</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2599371394348004</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.578093609073593</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-9.697259577044983</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Teknoloji</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>-2284321066.789329</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2568395234.075188</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1264359540.22262</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4122521667.570581</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1417738843.769765</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>44.4955306008557</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-45.88220524952462</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>PATEK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3963724062</v>
+      </c>
+      <c r="C26" t="n">
+        <v>674934433</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3622737714</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19.38999938964844</v>
+      </c>
+      <c r="F26" t="n">
+        <v>13086978243.92271</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9464240529.922714</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2692694176</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-700483262</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-432001509</v>
+      </c>
+      <c r="K26" t="n">
+        <v>537905795</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.32949852106113</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>3.514784788513136</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.301687513867789</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>-4.75158460772784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>19.9764904531067</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2592027804695328</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.406236196580121</v>
+      </c>
+      <c r="U26" t="n">
+        <v>12.45939927482637</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Teknoloji</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>27613515794.97206</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-7501395635.865675</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>23280919811.43605</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>36483371523.91905</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>19969102873.61537</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>29.58673005443682</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-34.46386486788958</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SEKTÖR TOPLAM</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>58169719774</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7570466316</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4861818731</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>535412522355.6246</v>
+      </c>
+      <c r="G27" t="n">
+        <v>530550703624.6246</v>
+      </c>
+      <c r="H27" t="n">
+        <v>72672578911</v>
+      </c>
+      <c r="I27" t="n">
+        <v>15057427371</v>
+      </c>
+      <c r="J27" t="n">
+        <v>20603735802</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10429729435</v>
+      </c>
+      <c r="L27" t="n">
+        <v>51.33522644977651</v>
+      </c>
+      <c r="M27" t="n">
+        <v>25.75021873330002</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.300562489661674</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9.204316686341283</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.02812303923104502</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Teknoloji</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>SEKTÖR Median</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1657125808</v>
-      </c>
-      <c r="C25" t="n">
-        <v>151264000</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-81046812</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>4696922041.538939</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4324761215.538939</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2294631332.5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>167273367.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>324899066</v>
-      </c>
-      <c r="K25" t="n">
-        <v>160965044</v>
-      </c>
-      <c r="L25" t="n">
-        <v>14.99485880229931</v>
-      </c>
-      <c r="M25" t="n">
-        <v>10.56256766907748</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.003523369564152</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.06837010811938</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.866559134142864</v>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>1914868068</v>
+      </c>
+      <c r="C28" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-82849116</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>7359710693.16864</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7044815164.16864</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2632002603</v>
+      </c>
+      <c r="I28" t="n">
+        <v>258629479</v>
+      </c>
+      <c r="J28" t="n">
+        <v>405049858</v>
+      </c>
+      <c r="K28" t="n">
+        <v>147651928</v>
+      </c>
+      <c r="L28" t="n">
+        <v>24.32949852106113</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10.69992892527193</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.895815409831297</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.653709948455729</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5.996738367981654</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
         <is>
           <t>Teknoloji</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
